--- a/data/Diessenhofen/investment_decision/Willisdorf_SFH_from_2015_investment_decision.xlsx
+++ b/data/Diessenhofen/investment_decision/Willisdorf_SFH_from_2015_investment_decision.xlsx
@@ -470,22 +470,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>12.66428611429295</v>
+        <v>1.962132581546066</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -545,19 +545,19 @@
         <v>3365.363125604972</v>
       </c>
       <c r="F3" t="n">
-        <v>12.66428611429295</v>
+        <v>1.962132581546066</v>
       </c>
       <c r="G3" t="n">
         <v>3365.363125604972</v>
       </c>
       <c r="H3" t="n">
-        <v>12.66428611429295</v>
+        <v>1.962132581546066</v>
       </c>
       <c r="I3" t="n">
         <v>3365.363125604972</v>
       </c>
       <c r="J3" t="n">
-        <v>12.66428611429295</v>
+        <v>1.962132581546066</v>
       </c>
       <c r="K3" t="n">
         <v>3365.363125604972</v>
@@ -568,7 +568,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>19.30923459779623</v>
+        <v>24.15048184459244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -582,19 +582,19 @@
         <v>3365.363125604972</v>
       </c>
       <c r="F4" t="n">
-        <v>19.50806482212519</v>
+        <v>23.71478194124514</v>
       </c>
       <c r="G4" t="n">
         <v>3365.363125604972</v>
       </c>
       <c r="H4" t="n">
-        <v>19.33565934423944</v>
+        <v>24.65943286378466</v>
       </c>
       <c r="I4" t="n">
         <v>3365.363125604972</v>
       </c>
       <c r="J4" t="n">
-        <v>19.33565934423944</v>
+        <v>24.58663176712155</v>
       </c>
       <c r="K4" t="n">
         <v>3365.363125604972</v>
@@ -605,7 +605,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>20.32627051176648</v>
+        <v>24.58887400569153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -619,19 +619,19 @@
         <v>3365.363125604972</v>
       </c>
       <c r="F5" t="n">
-        <v>20.32627051176648</v>
+        <v>24.2040934958125</v>
       </c>
       <c r="G5" t="n">
         <v>3365.363125604972</v>
       </c>
       <c r="H5" t="n">
-        <v>20.34324713226677</v>
+        <v>24.79157310638481</v>
       </c>
       <c r="I5" t="n">
         <v>3365.363125604972</v>
       </c>
       <c r="J5" t="n">
-        <v>20.28176899339812</v>
+        <v>24.73014379355311</v>
       </c>
       <c r="K5" t="n">
         <v>3365.363125604972</v>
@@ -642,7 +642,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>20.32627051176648</v>
+        <v>24.58887400569153</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -656,19 +656,19 @@
         <v>3365.363125604972</v>
       </c>
       <c r="F6" t="n">
-        <v>20.32627051176648</v>
+        <v>24.2040934958125</v>
       </c>
       <c r="G6" t="n">
         <v>3365.363125604972</v>
       </c>
       <c r="H6" t="n">
-        <v>20.34324713226677</v>
+        <v>24.79157310638481</v>
       </c>
       <c r="I6" t="n">
         <v>3365.363125604972</v>
       </c>
       <c r="J6" t="n">
-        <v>20.28176899339812</v>
+        <v>24.73014379355311</v>
       </c>
       <c r="K6" t="n">
         <v>3365.363125604972</v>
@@ -683,32 +683,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
     </row>
     <row r="8">
@@ -720,32 +720,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
     </row>
     <row r="9">
@@ -757,32 +757,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
     </row>
     <row r="10">
@@ -794,32 +794,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
     </row>
     <row r="11">
@@ -831,32 +831,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Willisdorf_b_SFH_from_2015</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Willisdorf_b_SFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5.048044688407458</v>
+        <v>8.17504179775281</v>
       </c>
     </row>
     <row r="12">
@@ -864,7 +864,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.001400686305882353</v>
+        <v>0.0008404117835294118</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,19 +878,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001400686305882353</v>
+        <v>0.0008404117835294118</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001470720621176471</v>
+        <v>0.0009104460988235294</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001470720621176471</v>
+        <v>0.0009104460988235294</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.001400686305882353</v>
+        <v>0.0009104460988235294</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -915,19 +915,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.001400686305882353</v>
+        <v>0.0009104460988235294</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001470720621176471</v>
+        <v>0.0009256720399999998</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001470720621176471</v>
+        <v>0.0009256720400000002</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -938,7 +938,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001470720621176477</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -952,19 +952,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001470720621176471</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001404134040433794</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001470720621176471</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -975,7 +975,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001470720621176476</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001470720621176471</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001404134040433794</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001470720621176471</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1012,7 +1012,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001470720621176477</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1026,19 +1026,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001470720621176471</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001404134040433794</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001750857882352941</v>
+        <v>0.001470720621176471</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1123,7 +1123,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.07441146000000014</v>
+        <v>0.09168111093396313</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         <v>1.250112528</v>
       </c>
       <c r="F19" t="n">
-        <v>0.07441146000000014</v>
+        <v>0.09898550955298956</v>
       </c>
       <c r="G19" t="n">
         <v>1.250112528</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07441146000000014</v>
+        <v>0.07346140497127622</v>
       </c>
       <c r="I19" t="n">
         <v>1.250112528</v>
       </c>
       <c r="J19" t="n">
-        <v>0.07441146000000014</v>
+        <v>0.07381171304021152</v>
       </c>
       <c r="K19" t="n">
         <v>1.250112528</v>
@@ -1160,7 +1160,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2071469704113462</v>
+        <v>0.09168111093396313</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,19 +1174,19 @@
         <v>1.250112528</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2071469704113462</v>
+        <v>0.09898550955298956</v>
       </c>
       <c r="G20" t="n">
         <v>1.250112528</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2071469704113461</v>
+        <v>0.07346140497127622</v>
       </c>
       <c r="I20" t="n">
         <v>1.250112528</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2071469704113461</v>
+        <v>0.07381171304021152</v>
       </c>
       <c r="K20" t="n">
         <v>1.250112528</v>
@@ -1197,7 +1197,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2071469704113462</v>
+        <v>0.09280359543408351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,19 +1211,19 @@
         <v>1.250112528</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2071469704113462</v>
+        <v>0.1015321491862547</v>
       </c>
       <c r="G21" t="n">
         <v>1.250112528</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2071469704113462</v>
+        <v>0.07346140497127622</v>
       </c>
       <c r="I21" t="n">
         <v>1.250112528</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2071469704113462</v>
+        <v>0.07732325263365813</v>
       </c>
       <c r="K21" t="n">
         <v>1.250112528</v>
@@ -1493,7 +1493,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.1764019727311189</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1507,19 +1507,19 @@
         <v>1.250112528</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.1751904800190582</v>
       </c>
       <c r="G29" t="n">
         <v>1.250112528</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.1868419638050787</v>
       </c>
       <c r="I29" t="n">
         <v>1.250112528</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.1873638234304123</v>
       </c>
       <c r="K29" t="n">
         <v>1.250112528</v>
@@ -1530,7 +1530,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.1778959565438533</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1544,19 +1544,19 @@
         <v>1.250112528</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.1780963210882015</v>
       </c>
       <c r="G30" t="n">
         <v>1.250112528</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.1868419638050787</v>
       </c>
       <c r="I30" t="n">
         <v>1.250112528</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.1873638234304123</v>
       </c>
       <c r="K30" t="n">
         <v>1.250112528</v>
@@ -1567,7 +1567,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.2032013117380294</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1581,19 +1581,19 @@
         <v>1.250112528</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.1984980343958216</v>
       </c>
       <c r="G31" t="n">
         <v>1.250112528</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.2183727938815615</v>
       </c>
       <c r="I31" t="n">
         <v>1.250112528</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.2145131476257698</v>
       </c>
       <c r="K31" t="n">
         <v>1.250112528</v>
@@ -2418,7 +2418,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>1.012748502996811</v>
+        <v>1.050754319210657</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2432,19 +2432,19 @@
         <v>6.387878775015163</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9868136030790986</v>
+        <v>1.036672319535499</v>
       </c>
       <c r="G54" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9812180538684495</v>
+        <v>1.04917505365079</v>
       </c>
       <c r="I54" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="J54" t="n">
-        <v>1.012571298128897</v>
+        <v>1.037193108319454</v>
       </c>
       <c r="K54" t="n">
         <v>6.387878775015163</v>
@@ -2455,7 +2455,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>1.012748502996811</v>
+        <v>1.050754319210657</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2469,19 +2469,19 @@
         <v>6.387878775015163</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9868136030790986</v>
+        <v>1.036672319535499</v>
       </c>
       <c r="G55" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9812180538684495</v>
+        <v>1.04917505365079</v>
       </c>
       <c r="I55" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="J55" t="n">
-        <v>1.012571298128897</v>
+        <v>1.037193108319454</v>
       </c>
       <c r="K55" t="n">
         <v>6.387878775015163</v>
@@ -2492,7 +2492,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>1.012748502996811</v>
+        <v>1.050754319210657</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2506,19 +2506,19 @@
         <v>6.387878775015163</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9868136030790986</v>
+        <v>1.036672319535499</v>
       </c>
       <c r="G56" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="H56" t="n">
-        <v>0.9812180538684495</v>
+        <v>1.04917505365079</v>
       </c>
       <c r="I56" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="J56" t="n">
-        <v>1.012571298128897</v>
+        <v>1.037193108319454</v>
       </c>
       <c r="K56" t="n">
         <v>6.387878775015163</v>
@@ -2771,7 +2771,7 @@
         <v>6.387878775015163</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1590446643325941</v>
+        <v>0.1590446643325942</v>
       </c>
       <c r="I63" t="n">
         <v>6.387878775015163</v>
@@ -2788,7 +2788,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.9997164153761521</v>
+        <v>0.2454274246039184</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2802,19 +2802,19 @@
         <v>6.387878775015163</v>
       </c>
       <c r="F64" t="n">
-        <v>1.021265354463079</v>
+        <v>0.2673597783346834</v>
       </c>
       <c r="G64" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="H64" t="n">
-        <v>1.030663965685913</v>
+        <v>0.2418093667633443</v>
       </c>
       <c r="I64" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9993107214254656</v>
+        <v>0.2511301730835523</v>
       </c>
       <c r="K64" t="n">
         <v>6.387878775015163</v>
@@ -2825,7 +2825,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.9772817996268081</v>
+        <v>0.2432793319853884</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2839,19 +2839,19 @@
         <v>6.387878775015163</v>
       </c>
       <c r="F65" t="n">
-        <v>1.003216699544521</v>
+        <v>0.2643053647511992</v>
       </c>
       <c r="G65" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="H65" t="n">
-        <v>1.008437764479428</v>
+        <v>0.2394284901979942</v>
       </c>
       <c r="I65" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="J65" t="n">
-        <v>0.9784406556352008</v>
+        <v>0.2485444019826867</v>
       </c>
       <c r="K65" t="n">
         <v>6.387878775015163</v>
@@ -2862,7 +2862,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.9772817996268081</v>
+        <v>0.2432793319853893</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2876,19 +2876,19 @@
         <v>6.387878775015163</v>
       </c>
       <c r="F66" t="n">
-        <v>1.003216699544521</v>
+        <v>0.2654391148758495</v>
       </c>
       <c r="G66" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="H66" t="n">
-        <v>1.008437764479428</v>
+        <v>0.2394284901979942</v>
       </c>
       <c r="I66" t="n">
         <v>6.387878775015163</v>
       </c>
       <c r="J66" t="n">
-        <v>0.9784406556352008</v>
+        <v>0.2485444019826867</v>
       </c>
       <c r="K66" t="n">
         <v>6.387878775015163</v>
